--- a/VerveStacks_UZB_grids_kan15/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_UZB_grids_kan15/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_UZB_grids_kan15\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0631FDD8-1F6F-460E-9758-EFBFE416E521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981EAD91-8797-46AA-B409-F5E588BA6CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -773,14 +773,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
   <dimension ref="B3:Y25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>20</v>
       </c>
@@ -788,7 +788,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>43</v>
       </c>
@@ -796,7 +796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>69</v>
       </c>
@@ -813,7 +813,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>31</v>
       </c>
@@ -875,7 +875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>86</v>
       </c>
@@ -904,10 +904,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O11" t="s">
         <v>119</v>
@@ -937,7 +937,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>86</v>
       </c>
@@ -966,10 +966,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="N12" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="O12" t="s">
         <v>119</v>
@@ -999,7 +999,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>86</v>
       </c>
@@ -1028,10 +1028,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="N13" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O13" t="s">
         <v>119</v>
@@ -1061,7 +1061,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>86</v>
       </c>
@@ -1090,10 +1090,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="N14" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="O14" t="s">
         <v>119</v>
@@ -1123,7 +1123,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>86</v>
       </c>
@@ -1152,10 +1152,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="N15" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="O15" t="s">
         <v>119</v>
@@ -1185,7 +1185,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>86</v>
       </c>
@@ -1214,10 +1214,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="N16" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="O16" t="s">
         <v>119</v>
@@ -1247,7 +1247,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>86</v>
       </c>
@@ -1276,10 +1276,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="N17" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="O17" t="s">
         <v>119</v>
@@ -1309,7 +1309,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>86</v>
       </c>
@@ -1338,10 +1338,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="N18" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="O18" t="s">
         <v>119</v>
@@ -1371,7 +1371,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>86</v>
       </c>
@@ -1400,10 +1400,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N19" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="O19" t="s">
         <v>119</v>
@@ -1433,7 +1433,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>86</v>
       </c>
@@ -1462,16 +1462,16 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="N20" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="O20" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>86</v>
       </c>
@@ -1500,16 +1500,16 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="N21" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="O21" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>86</v>
       </c>
@@ -1538,16 +1538,16 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N22" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="O22" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
       <c r="G23" t="s">
         <v>86</v>
       </c>
@@ -1564,16 +1564,16 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="N23" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="O23" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>86</v>
       </c>
@@ -1590,16 +1590,16 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="N24" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="O24" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>86</v>
       </c>
@@ -1616,10 +1616,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N25" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O25" t="s">
         <v>119</v>
@@ -1633,21 +1633,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3954DD3-0F24-46DF-B268-7A98442D0282}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.86328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1657,28 +1657,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C4:X57"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.265625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.86328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.06640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="4" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>4</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="5" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>3</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="6" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>6</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="7" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>7</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="8" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="9" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
         <v>9</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>10</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="11" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
         <v>6</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="12" spans="3:24" x14ac:dyDescent="0.25">
       <c r="P12" s="2" t="s">
         <v>26</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="13" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>4</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="14" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>3</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="15" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>11</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="16" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>6</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
         <v>13</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
         <v>13</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
         <v>7</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>8</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
         <v>9</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
         <v>10</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.25">
       <c r="P23" s="2" t="s">
         <v>30</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.25">
       <c r="P24" s="2" t="s">
         <v>30</v>
       </c>
@@ -2226,12 +2226,12 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>16</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>76</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>37</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
         <v>7</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D32" t="s">
         <v>10</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:22" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
         <v>9</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>17</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>85</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="38" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="3:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C38" t="s">
         <v>19</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="39" spans="3:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
         <v>20</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>14</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>15</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>41</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="3:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C43" t="s">
         <v>39</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="44" spans="3:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
         <v>40</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:22" x14ac:dyDescent="0.25">
       <c r="P45" t="s">
         <v>81</v>
       </c>
@@ -2479,12 +2479,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>1</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>48</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>53</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
         <v>48</v>
       </c>
@@ -2543,12 +2543,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>24</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="56" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
         <v>62</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
         <v>62</v>
       </c>
